--- a/analysis_files/pv_system_roi_analysis.xlsx
+++ b/analysis_files/pv_system_roi_analysis.xlsx
@@ -3097,13 +3097,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7000</v>
+        <v>13000</v>
       </c>
       <c r="C3" t="n">
         <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>1330</v>
+        <v>2470</v>
       </c>
       <c r="E3" t="n">
         <v>0.5</v>
@@ -3112,10 +3112,10 @@
         <v>0.5</v>
       </c>
       <c r="G3" t="n">
-        <v>665</v>
+        <v>1235</v>
       </c>
       <c r="H3" t="n">
-        <v>665</v>
+        <v>1235</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
